--- a/research/traditional_assets/database/data/italy/italy_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ17"/>
+  <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0916</v>
+        <v>0.0725</v>
       </c>
       <c r="E2">
-        <v>0.175</v>
+        <v>0.0373</v>
       </c>
       <c r="F2">
-        <v>0.06900000000000001</v>
+        <v>-0.01365</v>
       </c>
       <c r="G2">
-        <v>0.2159102714887211</v>
+        <v>0.379805568975336</v>
       </c>
       <c r="H2">
-        <v>0.2154169627406123</v>
+        <v>0.3795357978000262</v>
       </c>
       <c r="I2">
-        <v>0.2288735091119818</v>
+        <v>0.2844637714874037</v>
       </c>
       <c r="J2">
-        <v>0.2126742044481605</v>
+        <v>0.246276647635102</v>
       </c>
       <c r="K2">
-        <v>1312.242</v>
+        <v>1031.735</v>
       </c>
       <c r="L2">
-        <v>0.3036306089285644</v>
+        <v>0.2970462791443561</v>
       </c>
       <c r="M2">
-        <v>813.1292999999999</v>
+        <v>715.4118000000001</v>
       </c>
       <c r="N2">
-        <v>0.0609478240664398</v>
+        <v>0.06832211521932624</v>
       </c>
       <c r="O2">
-        <v>0.6196488909819987</v>
+        <v>0.6934065433468867</v>
       </c>
       <c r="P2">
-        <v>808.0592999999999</v>
+        <v>595.7318</v>
       </c>
       <c r="Q2">
-        <v>0.06056780397859295</v>
+        <v>0.05689262698688589</v>
       </c>
       <c r="R2">
-        <v>0.6157852743625032</v>
+        <v>0.5774077645907137</v>
       </c>
       <c r="S2">
-        <v>5.070000000000004</v>
+        <v>119.68</v>
       </c>
       <c r="T2">
-        <v>0.006235170716391605</v>
+        <v>0.1672882667017793</v>
       </c>
       <c r="U2">
-        <v>178.394</v>
+        <v>1004.869</v>
       </c>
       <c r="V2">
-        <v>0.01337146026653874</v>
+        <v>0.09596539447396468</v>
       </c>
       <c r="W2">
-        <v>0.02655750798722045</v>
+        <v>0.05359262008768154</v>
       </c>
       <c r="X2">
-        <v>0.06868529195867561</v>
+        <v>0.1024490019258407</v>
       </c>
       <c r="Y2">
-        <v>-0.04212778397145515</v>
+        <v>-0.04885638183815919</v>
       </c>
       <c r="Z2">
-        <v>0.6426718371828678</v>
+        <v>0.4757519262238889</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>-0.008930452435252948</v>
       </c>
       <c r="AB2">
-        <v>0.06088912712765356</v>
+        <v>0.09524628449478098</v>
       </c>
       <c r="AC2">
-        <v>-0.06526480952575946</v>
+        <v>-0.1039579625921551</v>
       </c>
       <c r="AD2">
-        <v>4983.837</v>
+        <v>3515.879</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4983.837</v>
+        <v>3515.879</v>
       </c>
       <c r="AG2">
-        <v>4805.442999999999</v>
+        <v>2511.01</v>
       </c>
       <c r="AH2">
-        <v>0.2719657595697125</v>
+        <v>0.2513669261950295</v>
       </c>
       <c r="AI2">
-        <v>0.4442131105444971</v>
+        <v>0.3939192946316341</v>
       </c>
       <c r="AJ2">
-        <v>0.2648087603998117</v>
+        <v>0.193419898214243</v>
       </c>
       <c r="AK2">
-        <v>0.4352330963305308</v>
+        <v>0.3170263025992013</v>
       </c>
       <c r="AL2">
-        <v>38.417</v>
+        <v>46.309</v>
       </c>
       <c r="AM2">
-        <v>7.717000000000002</v>
+        <v>30.396</v>
       </c>
       <c r="AN2">
-        <v>4.668244967235042</v>
+        <v>3.308187669896244</v>
       </c>
       <c r="AO2">
-        <v>25.74781997553167</v>
+        <v>21.33563670128917</v>
       </c>
       <c r="AP2">
-        <v>4.501147429196592</v>
+        <v>2.362678670393994</v>
       </c>
       <c r="AQ2">
-        <v>128.1785668005701</v>
+        <v>32.50532964863798</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>First Capital S.p.A. (BIT:FIC)</t>
+          <t>Innovative-RFK S.p.A. (ENXTPA:MLIRF)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,119 +724,101 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.9670000000000001</v>
-      </c>
       <c r="G3">
-        <v>0.2916666666666667</v>
+        <v>-3.929824561403509</v>
       </c>
       <c r="H3">
-        <v>0.2916666666666667</v>
+        <v>-3.929824561403509</v>
       </c>
       <c r="I3">
-        <v>0.8921568627450981</v>
+        <v>25.70175438596491</v>
       </c>
       <c r="J3">
-        <v>0.8488505747126437</v>
+        <v>25.70175438596491</v>
       </c>
       <c r="K3">
-        <v>34.3</v>
+        <v>2.96</v>
       </c>
       <c r="L3">
-        <v>0.8406862745098039</v>
+        <v>25.96491228070175</v>
       </c>
       <c r="M3">
-        <v>3.235</v>
+        <v>8.98</v>
       </c>
       <c r="N3">
-        <v>0.05038940809968848</v>
+        <v>0.4961325966850829</v>
       </c>
       <c r="O3">
-        <v>0.09431486880466473</v>
+        <v>3.033783783783784</v>
       </c>
       <c r="P3">
-        <v>0.095</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.001479750778816199</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.002769679300291545</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>3.14</v>
+        <v>8.98</v>
       </c>
       <c r="T3">
-        <v>0.9706336939721792</v>
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0.001</v>
+        <v>7.52</v>
       </c>
       <c r="V3">
-        <v>1.557632398753894e-05</v>
-      </c>
-      <c r="W3">
-        <v>0.6520912547528517</v>
+        <v>0.4154696132596685</v>
       </c>
       <c r="X3">
-        <v>0.07836200358935676</v>
-      </c>
-      <c r="Y3">
-        <v>0.5737292511634949</v>
-      </c>
-      <c r="Z3">
-        <v>0.5190905736714208</v>
-      </c>
-      <c r="AA3">
-        <v>0.4406303317889014</v>
+        <v>0.102390485135889</v>
       </c>
       <c r="AB3">
-        <v>0.06175641290922983</v>
-      </c>
-      <c r="AC3">
-        <v>0.3788739188796716</v>
+        <v>0.09620834182750405</v>
       </c>
       <c r="AD3">
-        <v>35.8</v>
+        <v>3.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>35.8</v>
+        <v>3.6</v>
       </c>
       <c r="AG3">
-        <v>35.799</v>
+        <v>-3.919999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.358</v>
+        <v>0.1658986175115207</v>
       </c>
       <c r="AI3">
-        <v>0.283452098178939</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="AJ3">
-        <v>0.3579935799357994</v>
+        <v>-0.2764456981664316</v>
       </c>
       <c r="AK3">
-        <v>0.2834464247539569</v>
+        <v>-0.4091858037578288</v>
       </c>
       <c r="AL3">
-        <v>1.55</v>
+        <v>0.102</v>
       </c>
       <c r="AM3">
-        <v>1.55</v>
+        <v>0.102</v>
       </c>
       <c r="AN3">
-        <v>0.9835164835164835</v>
+        <v>1.228668941979522</v>
       </c>
       <c r="AO3">
-        <v>23.48387096774193</v>
+        <v>28.72549019607844</v>
       </c>
       <c r="AP3">
-        <v>0.983489010989011</v>
+        <v>-1.337883959044368</v>
       </c>
       <c r="AQ3">
-        <v>23.48387096774193</v>
+        <v>28.72549019607844</v>
       </c>
     </row>
     <row r="4">
@@ -856,124 +838,124 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.135</v>
+        <v>0.131</v>
       </c>
       <c r="E4">
-        <v>0.242</v>
+        <v>0.23</v>
       </c>
       <c r="F4">
-        <v>0.06900000000000001</v>
+        <v>-0.058</v>
       </c>
       <c r="G4">
-        <v>0.3402637519306166</v>
+        <v>0.4927887388946579</v>
       </c>
       <c r="H4">
-        <v>0.3402637519306166</v>
+        <v>0.4927887388946579</v>
       </c>
       <c r="I4">
-        <v>0.3669359629321611</v>
+        <v>0.4485404407522787</v>
       </c>
       <c r="J4">
-        <v>0.3394986301401444</v>
+        <v>0.3371254378734055</v>
       </c>
       <c r="K4">
-        <v>549.3</v>
+        <v>573.9</v>
       </c>
       <c r="L4">
-        <v>0.3263039087560888</v>
+        <v>0.3310834198684666</v>
       </c>
       <c r="M4">
-        <v>224.1</v>
+        <v>275.08</v>
       </c>
       <c r="N4">
-        <v>0.05744386342663796</v>
+        <v>0.08841320348407419</v>
       </c>
       <c r="O4">
-        <v>0.4079737848170399</v>
+        <v>0.479316954173201</v>
       </c>
       <c r="P4">
-        <v>224.1</v>
+        <v>267.6</v>
       </c>
       <c r="Q4">
-        <v>0.05744386342663796</v>
+        <v>0.08600906373541607</v>
       </c>
       <c r="R4">
-        <v>0.4079737848170399</v>
+        <v>0.4662833246210142</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>7.480000000000018</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.02719208957394219</v>
       </c>
       <c r="U4">
-        <v>0.028</v>
+        <v>312.1</v>
       </c>
       <c r="V4">
-        <v>7.17727878601456e-06</v>
+        <v>0.100311766785588</v>
       </c>
       <c r="W4">
-        <v>0.6417056074766354</v>
+        <v>0.5463112803426939</v>
       </c>
       <c r="X4">
-        <v>0.06896924592130119</v>
+        <v>0.1019395004499822</v>
       </c>
       <c r="Y4">
-        <v>0.5727363615553343</v>
+        <v>0.4443717798927117</v>
       </c>
       <c r="Z4">
-        <v>1.260626284290173</v>
+        <v>1.223658239750609</v>
       </c>
       <c r="AA4">
-        <v>0.4279808966351741</v>
+        <v>0.4125263198833247</v>
       </c>
       <c r="AB4">
-        <v>0.06088912712765356</v>
+        <v>0.09472574811939445</v>
       </c>
       <c r="AC4">
-        <v>0.3670917695075205</v>
+        <v>0.3178005717639303</v>
       </c>
       <c r="AD4">
-        <v>1090.3</v>
+        <v>585.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1090.3</v>
+        <v>585.4</v>
       </c>
       <c r="AG4">
-        <v>1090.272</v>
+        <v>273.3</v>
       </c>
       <c r="AH4">
-        <v>0.2184313332665531</v>
+        <v>0.1583574539454108</v>
       </c>
       <c r="AI4">
-        <v>0.4967424484031164</v>
+        <v>0.3044043471478342</v>
       </c>
       <c r="AJ4">
-        <v>0.2184269490042216</v>
+        <v>0.08074809430951957</v>
       </c>
       <c r="AK4">
-        <v>0.4967360283424272</v>
+        <v>0.1696461824953445</v>
       </c>
       <c r="AL4">
-        <v>19.5</v>
+        <v>12.2</v>
       </c>
       <c r="AM4">
-        <v>19.5</v>
+        <v>12.2</v>
       </c>
       <c r="AN4">
-        <v>1.72707112307936</v>
+        <v>0.7248637939574046</v>
       </c>
       <c r="AO4">
-        <v>31.67692307692308</v>
+        <v>63.72950819672131</v>
       </c>
       <c r="AP4">
-        <v>1.727026770156819</v>
+        <v>0.338410104011887</v>
       </c>
       <c r="AQ4">
-        <v>31.67692307692308</v>
+        <v>63.72950819672131</v>
       </c>
     </row>
     <row r="5">
@@ -993,124 +975,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0916</v>
+        <v>0.0736</v>
       </c>
       <c r="E5">
-        <v>0.194</v>
-      </c>
-      <c r="F5">
-        <v>0.038</v>
+        <v>0.0508</v>
       </c>
       <c r="G5">
-        <v>0.2619168910559639</v>
+        <v>0.4052402555318952</v>
       </c>
       <c r="H5">
-        <v>0.2619168910559639</v>
+        <v>0.4052402555318952</v>
       </c>
       <c r="I5">
-        <v>0.2660650607670476</v>
+        <v>0.2311822979353764</v>
       </c>
       <c r="J5">
-        <v>0.2028075175011068</v>
+        <v>0.1525197266089695</v>
       </c>
       <c r="K5">
-        <v>264.7</v>
+        <v>146</v>
       </c>
       <c r="L5">
-        <v>0.1926351793901463</v>
+        <v>0.1351726691972966</v>
       </c>
       <c r="M5">
-        <v>91.3</v>
+        <v>196.3</v>
       </c>
       <c r="N5">
-        <v>0.050584519918001</v>
+        <v>0.1500879272115605</v>
       </c>
       <c r="O5">
-        <v>0.3449187759727994</v>
+        <v>1.344520547945206</v>
       </c>
       <c r="P5">
-        <v>91.3</v>
+        <v>93.3</v>
       </c>
       <c r="Q5">
-        <v>0.050584519918001</v>
+        <v>0.0713357290312715</v>
       </c>
       <c r="R5">
-        <v>0.3449187759727994</v>
+        <v>0.6390410958904109</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.5247070809984717</v>
       </c>
       <c r="U5">
-        <v>0.006</v>
+        <v>540.8</v>
       </c>
       <c r="V5">
-        <v>3.324283893844534e-06</v>
+        <v>0.4134872696689349</v>
       </c>
       <c r="W5">
-        <v>0.1790933694181326</v>
+        <v>0.08913853104585139</v>
       </c>
       <c r="X5">
-        <v>0.07612493632418287</v>
+        <v>0.1161535431174833</v>
       </c>
       <c r="Y5">
-        <v>0.1029684330939497</v>
+        <v>-0.02701501207163194</v>
       </c>
       <c r="Z5">
-        <v>1.641906432483005</v>
+        <v>0.8686008939327408</v>
       </c>
       <c r="AA5">
-        <v>0.3329909675409771</v>
+        <v>0.1324787708749281</v>
       </c>
       <c r="AB5">
-        <v>0.0615792016270977</v>
+        <v>0.09553358619858679</v>
       </c>
       <c r="AC5">
-        <v>0.2714117659138794</v>
+        <v>0.03694518467634134</v>
       </c>
       <c r="AD5">
-        <v>886.9</v>
+        <v>688.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>886.9</v>
+        <v>688.9</v>
       </c>
       <c r="AG5">
-        <v>886.894</v>
+        <v>148.1</v>
       </c>
       <c r="AH5">
-        <v>0.3294821309161156</v>
+        <v>0.3450020032051281</v>
       </c>
       <c r="AI5">
-        <v>0.3512753485424588</v>
+        <v>0.3369857652986352</v>
       </c>
       <c r="AJ5">
-        <v>0.3294806363339839</v>
+        <v>0.101717032967033</v>
       </c>
       <c r="AK5">
-        <v>0.3512738068927604</v>
+        <v>0.09850349185234454</v>
       </c>
       <c r="AL5">
-        <v>13.8</v>
+        <v>12.5</v>
       </c>
       <c r="AM5">
-        <v>13.8</v>
+        <v>12.5</v>
       </c>
       <c r="AN5">
-        <v>2.123802681992337</v>
+        <v>2.376336667816489</v>
       </c>
       <c r="AO5">
-        <v>26.49275362318841</v>
+        <v>19.976</v>
       </c>
       <c r="AP5">
-        <v>2.123788314176245</v>
+        <v>0.5108658157985514</v>
       </c>
       <c r="AQ5">
-        <v>26.49275362318841</v>
+        <v>19.976</v>
       </c>
     </row>
     <row r="6">
@@ -1121,7 +1100,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DeA Capital S.p.A. (BIT:DEA)</t>
+          <t>LVenture Group S.p.A. (BIT:LVEN)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1130,115 +1109,115 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0636</v>
+        <v>0.375</v>
       </c>
       <c r="G6">
-        <v>0.0566006600660066</v>
+        <v>0.2281553398058252</v>
       </c>
       <c r="H6">
-        <v>0.0566006600660066</v>
+        <v>0.2281553398058252</v>
       </c>
       <c r="I6">
-        <v>0.363036303630363</v>
+        <v>0.270873786407767</v>
       </c>
       <c r="J6">
-        <v>0.363036303630363</v>
+        <v>0.270873786407767</v>
       </c>
       <c r="K6">
-        <v>49.8</v>
+        <v>2.67</v>
       </c>
       <c r="L6">
-        <v>0.4108910891089109</v>
+        <v>0.2592233009708738</v>
       </c>
       <c r="M6">
-        <v>32.13</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.08304471439648489</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.6451807228915664</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>30.2</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.07805634530886535</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.606425702811245</v>
+        <v>-0</v>
       </c>
       <c r="S6">
-        <v>1.930000000000003</v>
-      </c>
-      <c r="T6">
-        <v>0.06006847183317781</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>147.5</v>
+        <v>2.18</v>
       </c>
       <c r="V6">
-        <v>0.3812354613595245</v>
+        <v>0.1058252427184466</v>
       </c>
       <c r="W6">
-        <v>0.09954027583449929</v>
+        <v>0.1080971659919028</v>
       </c>
       <c r="X6">
-        <v>0.06076241598006991</v>
+        <v>0.1067370405241838</v>
       </c>
       <c r="Y6">
-        <v>0.03877785985442938</v>
+        <v>0.001360125467718992</v>
       </c>
       <c r="Z6">
-        <v>0.4649021864211737</v>
+        <v>0.3510565780504431</v>
       </c>
       <c r="AA6">
-        <v>0.1687763713080168</v>
+        <v>0.09509202453987731</v>
       </c>
       <c r="AB6">
-        <v>0.05975028408734619</v>
+        <v>0.09504536660762546</v>
       </c>
       <c r="AC6">
-        <v>0.1090260872206707</v>
+        <v>4.665793225185066e-05</v>
       </c>
       <c r="AD6">
-        <v>14.1</v>
+        <v>6.23</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>14.1</v>
+        <v>6.23</v>
       </c>
       <c r="AG6">
-        <v>-133.4</v>
+        <v>4.050000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.03516209476309227</v>
+        <v>0.2322027581065971</v>
       </c>
       <c r="AI6">
-        <v>0.02580527086383602</v>
+        <v>0.1763373903198415</v>
       </c>
       <c r="AJ6">
-        <v>-0.5262327416173571</v>
+        <v>0.1643002028397566</v>
       </c>
       <c r="AK6">
-        <v>-0.3344196540486338</v>
+        <v>0.1221719457013575</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>0.155</v>
       </c>
       <c r="AM6">
-        <v>-2.77</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AN6">
-        <v>0.282565130260521</v>
+        <v>2.076666666666667</v>
+      </c>
+      <c r="AO6">
+        <v>18</v>
       </c>
       <c r="AP6">
-        <v>-2.673346693386774</v>
+        <v>1.35</v>
       </c>
       <c r="AQ6">
-        <v>-15.88447653429603</v>
+        <v>32.06896551724138</v>
       </c>
     </row>
     <row r="7">
@@ -1249,7 +1228,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Solutions Capital Management SIM S.p.A. (BIT:SCM)</t>
+          <t>Banca Generali S.p.A. (BIT:BGN)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1258,47 +1237,56 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0334</v>
+        <v>0.07139999999999999</v>
+      </c>
+      <c r="E7">
+        <v>0.0238</v>
+      </c>
+      <c r="F7">
+        <v>0.0307</v>
       </c>
       <c r="G7">
-        <v>-0.01186224489795918</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>-0.01186224489795918</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>0.04668367346938775</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>0.04668367346938775</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>0.28</v>
+        <v>203.6</v>
       </c>
       <c r="L7">
-        <v>0.03571428571428572</v>
+        <v>0.3635714285714285</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>216.785</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.05574168830834898</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>1.064759332023576</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>216.785</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.05574168830834898</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>1.064759332023576</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
         <v>0</v>
       </c>
@@ -1306,67 +1294,55 @@
         <v>0</v>
       </c>
       <c r="W7">
-        <v>0.08562691131498472</v>
+        <v>0.1680422581710135</v>
       </c>
       <c r="X7">
-        <v>0.06141827450523805</v>
+        <v>0.112796577471788</v>
       </c>
       <c r="Y7">
-        <v>0.02420863680974667</v>
+        <v>0.05524568069922549</v>
       </c>
       <c r="Z7">
-        <v>2.022703818369453</v>
+        <v>0.2347811504276371</v>
       </c>
       <c r="AA7">
-        <v>0.09442724458204334</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06016877461312951</v>
+        <v>0.09537690063297448</v>
       </c>
       <c r="AC7">
-        <v>0.03425846996891383</v>
+        <v>-0.09537690063297448</v>
       </c>
       <c r="AD7">
-        <v>0.5</v>
+        <v>1737.5</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.5</v>
+        <v>1737.5</v>
       </c>
       <c r="AG7">
-        <v>0.5</v>
+        <v>1737.5</v>
       </c>
       <c r="AH7">
-        <v>0.05291005291005291</v>
+        <v>0.3088010521451676</v>
       </c>
       <c r="AI7">
-        <v>0.1184834123222749</v>
+        <v>0.6355157278712509</v>
       </c>
       <c r="AJ7">
-        <v>0.05291005291005291</v>
+        <v>0.3088010521451676</v>
       </c>
       <c r="AK7">
-        <v>0.1184834123222749</v>
+        <v>0.6355157278712509</v>
       </c>
       <c r="AL7">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>0.03</v>
-      </c>
-      <c r="AN7">
-        <v>1.193317422434368</v>
-      </c>
-      <c r="AO7">
-        <v>12.2</v>
-      </c>
-      <c r="AP7">
-        <v>1.193317422434368</v>
-      </c>
-      <c r="AQ7">
-        <v>12.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1386,7 +1362,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0611</v>
+        <v>0.00465</v>
+      </c>
+      <c r="E8">
+        <v>-0.216</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1401,10 +1380,10 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0.806</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L8">
-        <v>0.2196185286103542</v>
+        <v>0.02871621621621622</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1428,55 +1407,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0.868</v>
+        <v>0.516</v>
       </c>
       <c r="V8">
-        <v>0.1366929133858268</v>
+        <v>0.1240384615384615</v>
       </c>
       <c r="W8">
-        <v>0.2322766570605187</v>
+        <v>0.01804670912951168</v>
       </c>
       <c r="X8">
-        <v>0.06570045646526927</v>
+        <v>0.1025075187157925</v>
       </c>
       <c r="Y8">
-        <v>0.1665762005952495</v>
+        <v>-0.0844608095862808</v>
       </c>
       <c r="Z8">
-        <v>2.876175548589341</v>
+        <v>1.297107800175285</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06049161094114271</v>
+        <v>0.09574892482255891</v>
       </c>
       <c r="AC8">
-        <v>-0.06049161094114271</v>
+        <v>-0.09574892482255891</v>
       </c>
       <c r="AD8">
-        <v>1.16</v>
+        <v>0.839</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.16</v>
+        <v>0.839</v>
       </c>
       <c r="AG8">
-        <v>0.2919999999999999</v>
+        <v>0.323</v>
       </c>
       <c r="AH8">
-        <v>0.1544607190412783</v>
+        <v>0.1678335667133427</v>
       </c>
       <c r="AI8">
-        <v>0.1976149914821124</v>
+        <v>0.165515880844348</v>
       </c>
       <c r="AJ8">
-        <v>0.04396266184884071</v>
+        <v>0.0720499665402632</v>
       </c>
       <c r="AK8">
-        <v>0.05837664934026388</v>
+        <v>0.07094223588842519</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1493,7 +1472,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A. (BIT:BGN)</t>
+          <t>DeA Capital S.p.A. (BIT:DEA)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1502,112 +1481,118 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.136</v>
+        <v>-0.0132</v>
       </c>
       <c r="E9">
-        <v>0.175</v>
-      </c>
-      <c r="F9">
-        <v>0.07049999999999999</v>
+        <v>-0.42</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.6402877697841727</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>0.6402877697841727</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>-0.0223021582733813</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>-0.01115107913669065</v>
       </c>
       <c r="K9">
-        <v>405.7</v>
+        <v>0.483</v>
       </c>
       <c r="L9">
-        <v>0.4401649126613865</v>
+        <v>0.006949640287769784</v>
       </c>
       <c r="M9">
-        <v>437.7719999999999</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.08704258957330893</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>1.079053487798866</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>437.7719999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.08704258957330893</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>1.079053487798866</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>0.2064439140811456</v>
       </c>
       <c r="W9">
-        <v>0.3235763279629925</v>
+        <v>0.0009415204678362573</v>
       </c>
       <c r="X9">
-        <v>0.06741151426093554</v>
+        <v>0.09508239443788688</v>
       </c>
       <c r="Y9">
-        <v>0.256164813702057</v>
+        <v>-0.09414087397005062</v>
       </c>
       <c r="Z9">
-        <v>0.4015772046009063</v>
+        <v>0.2634571645185746</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>-0.002937831690674754</v>
       </c>
       <c r="AB9">
-        <v>0.06070747473444584</v>
+        <v>0.09414517144837756</v>
       </c>
       <c r="AC9">
-        <v>-0.06070747473444584</v>
+        <v>-0.09708300313905231</v>
       </c>
       <c r="AD9">
-        <v>1173.6</v>
+        <v>10.4</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>1173.6</v>
+        <v>10.4</v>
       </c>
       <c r="AG9">
-        <v>1173.6</v>
+        <v>-76.09999999999999</v>
       </c>
       <c r="AH9">
-        <v>0.1891987747863937</v>
+        <v>0.02421984163949698</v>
       </c>
       <c r="AI9">
-        <v>0.4919723328442674</v>
+        <v>0.02395209580838323</v>
       </c>
       <c r="AJ9">
-        <v>0.1891987747863937</v>
+        <v>-0.2219305920093322</v>
       </c>
       <c r="AK9">
-        <v>0.4919723328442674</v>
+        <v>-0.2188668392292205</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>0.285</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>-0.207</v>
+      </c>
+      <c r="AN9">
+        <v>15.45319465081724</v>
+      </c>
+      <c r="AO9">
+        <v>-5.438596491228071</v>
+      </c>
+      <c r="AP9">
+        <v>-113.075780089153</v>
+      </c>
+      <c r="AQ9">
+        <v>7.487922705314009</v>
       </c>
     </row>
     <row r="10">
@@ -1618,7 +1603,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Banca Finnat Euramerica S.p.A. (BIT:BFE)</t>
+          <t>First Capital S.p.A. (BIT:FIC)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1626,110 +1611,98 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D10">
-        <v>-0.00108</v>
-      </c>
-      <c r="E10">
-        <v>-0.131</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
       <c r="K10">
-        <v>6.07</v>
-      </c>
-      <c r="L10">
-        <v>0.08071808510638298</v>
+        <v>-4.41</v>
       </c>
       <c r="M10">
-        <v>5.0115</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.04981610337972167</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.8256177924217463</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>5.0115</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.04981610337972167</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.8256177924217463</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>1.05</v>
+        <v>5.99</v>
       </c>
       <c r="V10">
-        <v>0.01043737574552684</v>
+        <v>0.1079279279279279</v>
       </c>
       <c r="W10">
-        <v>0.02354538401861908</v>
+        <v>-0.0504</v>
       </c>
       <c r="X10">
-        <v>0.4619971931909631</v>
+        <v>0.1259622935651854</v>
       </c>
       <c r="Y10">
-        <v>-0.4384518091723439</v>
+        <v>-0.1763622935651854</v>
       </c>
       <c r="Z10">
-        <v>0.2970242280134925</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>-0.01492307317983114</v>
       </c>
       <c r="AB10">
-        <v>0.06526480952575946</v>
+        <v>0.09590984886542675</v>
       </c>
       <c r="AC10">
-        <v>-0.06526480952575946</v>
+        <v>-0.1108329220452579</v>
       </c>
       <c r="AD10">
-        <v>1199</v>
+        <v>42.2</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>1199</v>
+        <v>42.2</v>
       </c>
       <c r="AG10">
-        <v>1197.95</v>
+        <v>36.21</v>
       </c>
       <c r="AH10">
-        <v>0.922591566635888</v>
+        <v>0.4319344933469806</v>
       </c>
       <c r="AI10">
-        <v>0.8015777510362349</v>
+        <v>0.3403225806451613</v>
       </c>
       <c r="AJ10">
-        <v>0.922528974625544</v>
+        <v>0.3948315341838403</v>
       </c>
       <c r="AK10">
-        <v>0.8014383676200034</v>
+        <v>0.306838403525125</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>3.16</v>
+      </c>
+      <c r="AN10">
+        <v>-23.18681318681319</v>
+      </c>
+      <c r="AO10">
+        <v>-0.5822784810126582</v>
+      </c>
+      <c r="AP10">
+        <v>-19.89560439560439</v>
+      </c>
+      <c r="AQ10">
+        <v>-0.5822784810126582</v>
       </c>
     </row>
     <row r="11">
@@ -1749,46 +1722,46 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.167</v>
+        <v>-0.141</v>
       </c>
       <c r="E11">
-        <v>-0.152</v>
+        <v>0.156</v>
       </c>
       <c r="G11">
-        <v>-2.364273204903678</v>
+        <v>-16.43292682926829</v>
       </c>
       <c r="H11">
-        <v>-2.364273204903678</v>
+        <v>-16.43292682926829</v>
       </c>
       <c r="I11">
-        <v>-9.859894921190893</v>
+        <v>-8.871951219512196</v>
       </c>
       <c r="J11">
-        <v>-9.859894921190893</v>
+        <v>-8.871951219512196</v>
       </c>
       <c r="K11">
-        <v>26.6</v>
+        <v>123.9</v>
       </c>
       <c r="L11">
-        <v>4.658493870402802</v>
+        <v>37.77439024390245</v>
       </c>
       <c r="M11">
-        <v>19.5808</v>
+        <v>18.0468</v>
       </c>
       <c r="N11">
-        <v>0.01031436999578593</v>
+        <v>0.01382578717536198</v>
       </c>
       <c r="O11">
-        <v>0.7361203007518798</v>
+        <v>0.1456561743341404</v>
       </c>
       <c r="P11">
-        <v>19.5808</v>
+        <v>18.0468</v>
       </c>
       <c r="Q11">
-        <v>0.01031436999578593</v>
+        <v>0.01382578717536198</v>
       </c>
       <c r="R11">
-        <v>0.7361203007518798</v>
+        <v>0.1456561743341404</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1797,73 +1770,73 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>4.17</v>
+        <v>35</v>
       </c>
       <c r="V11">
-        <v>0.002196586599241466</v>
+        <v>0.02681375928905233</v>
       </c>
       <c r="W11">
-        <v>0.02655750798722045</v>
+        <v>0.0989142583426473</v>
       </c>
       <c r="X11">
-        <v>0.06917805133513923</v>
+        <v>0.1079187752605475</v>
       </c>
       <c r="Y11">
-        <v>-0.04262054334791877</v>
+        <v>-0.009004516917900218</v>
       </c>
       <c r="Z11">
-        <v>0.003558696681873707</v>
+        <v>0.0018433904896787</v>
       </c>
       <c r="AA11">
-        <v>-0.03508837533966545</v>
+        <v>-0.01635447050294212</v>
       </c>
       <c r="AB11">
-        <v>0.06091248585403769</v>
+        <v>0.09511566835658747</v>
       </c>
       <c r="AC11">
-        <v>-0.09600086119370313</v>
+        <v>-0.1114701388595296</v>
       </c>
       <c r="AD11">
-        <v>542.3</v>
+        <v>431.5</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>542.3</v>
+        <v>431.5</v>
       </c>
       <c r="AG11">
-        <v>538.13</v>
+        <v>396.5</v>
       </c>
       <c r="AH11">
-        <v>0.2221903552259598</v>
+        <v>0.2484454168585905</v>
       </c>
       <c r="AI11">
-        <v>0.2949847693646649</v>
+        <v>0.278207607994842</v>
       </c>
       <c r="AJ11">
-        <v>0.2208591726758956</v>
+        <v>0.2329886003055588</v>
       </c>
       <c r="AK11">
-        <v>0.293381964093925</v>
+        <v>0.2615435356200528</v>
       </c>
       <c r="AL11">
-        <v>1.56</v>
+        <v>11.4</v>
       </c>
       <c r="AM11">
-        <v>-26.34</v>
+        <v>-3.9</v>
       </c>
       <c r="AN11">
-        <v>-9.649466192170816</v>
+        <v>-14.87931034482759</v>
       </c>
       <c r="AO11">
-        <v>-36.08974358974358</v>
+        <v>-2.552631578947369</v>
       </c>
       <c r="AP11">
-        <v>-9.57526690391459</v>
+        <v>-13.67241379310345</v>
       </c>
       <c r="AQ11">
-        <v>2.137433561123766</v>
+        <v>7.461538461538461</v>
       </c>
     </row>
     <row r="12">
@@ -1874,7 +1847,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Copernico Sim S.p.A. (BIT:COP)</t>
+          <t>Digital Magics S.p.A. (BIT:DM)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1882,32 +1855,35 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D12">
+        <v>0.104</v>
+      </c>
       <c r="G12">
-        <v>0.002183406113537117</v>
+        <v>-0.1744525547445256</v>
       </c>
       <c r="H12">
-        <v>-0.01681222707423581</v>
+        <v>-0.3941605839416059</v>
       </c>
       <c r="I12">
-        <v>-0.03897379912663755</v>
+        <v>-0.2822384428223844</v>
       </c>
       <c r="J12">
-        <v>-0.03897379912663755</v>
+        <v>-0.2822384428223844</v>
       </c>
       <c r="K12">
-        <v>-0.331</v>
+        <v>-1.67</v>
       </c>
       <c r="L12">
-        <v>-0.0361353711790393</v>
+        <v>-0.4063260340632603</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>0.22</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.005759162303664921</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>-0.1317365269461078</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1919,76 +1895,79 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>0.22</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
       </c>
       <c r="U12">
-        <v>0.001</v>
+        <v>9.83</v>
       </c>
       <c r="V12">
-        <v>7.692307692307693e-05</v>
+        <v>0.2573298429319372</v>
       </c>
       <c r="W12">
-        <v>-0.06304761904761905</v>
+        <v>-0.08391959798994975</v>
       </c>
       <c r="X12">
-        <v>0.06082276790804854</v>
+        <v>0.09918376814089064</v>
       </c>
       <c r="Y12">
-        <v>-0.1238703869556676</v>
+        <v>-0.1831033661308404</v>
       </c>
       <c r="Z12">
-        <v>1.578765942778352</v>
+        <v>0.1843049327354261</v>
       </c>
       <c r="AA12">
-        <v>-0.06153050672182006</v>
+        <v>-0.05201793721973094</v>
       </c>
       <c r="AB12">
-        <v>0.05976060501064683</v>
+        <v>0.0945127320589656</v>
       </c>
       <c r="AC12">
-        <v>-0.1212911117324669</v>
+        <v>-0.1465306692786965</v>
       </c>
       <c r="AD12">
-        <v>0.497</v>
+        <v>4.68</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0.497</v>
+        <v>4.68</v>
       </c>
       <c r="AG12">
-        <v>0.496</v>
+        <v>-5.15</v>
       </c>
       <c r="AH12">
-        <v>0.03682299770319331</v>
+        <v>0.1091417910447761</v>
       </c>
       <c r="AI12">
-        <v>0.08723889766543795</v>
+        <v>0.149616368286445</v>
       </c>
       <c r="AJ12">
-        <v>0.03675163011262596</v>
+        <v>-0.1558245083207262</v>
       </c>
       <c r="AK12">
-        <v>0.08707865168539326</v>
+        <v>-0.2400932400932401</v>
       </c>
       <c r="AL12">
-        <v>0.07099999999999999</v>
+        <v>0.099</v>
       </c>
       <c r="AM12">
-        <v>0.07099999999999999</v>
+        <v>0.06100000000000001</v>
       </c>
       <c r="AN12">
-        <v>-2.88953488372093</v>
+        <v>-4.141592920353983</v>
       </c>
       <c r="AO12">
-        <v>-5.028169014084507</v>
+        <v>-11.71717171717172</v>
       </c>
       <c r="AP12">
-        <v>-2.883720930232558</v>
+        <v>4.557522123893806</v>
       </c>
       <c r="AQ12">
-        <v>-5.028169014084507</v>
+        <v>-19.01639344262295</v>
       </c>
     </row>
     <row r="13">
@@ -1999,7 +1978,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Digital Magics S.p.A. (BIT:DM)</t>
+          <t>Solutions Capital Management SIM S.p.A. (BIT:SCM)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2008,25 +1987,25 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.0295</v>
+        <v>-0.0578</v>
       </c>
       <c r="G13">
-        <v>-0.1731800766283525</v>
+        <v>-0.01663920922570017</v>
       </c>
       <c r="H13">
-        <v>-0.4367816091954023</v>
+        <v>-0.02224052718286656</v>
       </c>
       <c r="I13">
-        <v>-0.632183908045977</v>
+        <v>-0.1067545304777595</v>
       </c>
       <c r="J13">
-        <v>-0.632183908045977</v>
+        <v>-0.1067545304777595</v>
       </c>
       <c r="K13">
-        <v>-3.35</v>
+        <v>-0.763</v>
       </c>
       <c r="L13">
-        <v>-1.28352490421456</v>
+        <v>-0.1257001647446458</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -2050,73 +2029,73 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>0.1148606811145511</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>-0.179144385026738</v>
+        <v>-0.2051075268817204</v>
       </c>
       <c r="X13">
-        <v>0.06716359783047639</v>
+        <v>0.09989315329693996</v>
       </c>
       <c r="Y13">
-        <v>-0.2463079828572144</v>
+        <v>-0.3050006801786604</v>
       </c>
       <c r="Z13">
-        <v>0.1245110199408453</v>
+        <v>1.438388625592417</v>
       </c>
       <c r="AA13">
-        <v>-0.07871386318099417</v>
+        <v>-0.1535545023696682</v>
       </c>
       <c r="AB13">
-        <v>0.06067730343719521</v>
+        <v>0.09563927748718161</v>
       </c>
       <c r="AC13">
-        <v>-0.1393911666181894</v>
+        <v>-0.2491937798568498</v>
       </c>
       <c r="AD13">
-        <v>7.3</v>
+        <v>1.04</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>7.3</v>
+        <v>1.04</v>
       </c>
       <c r="AG13">
-        <v>3.59</v>
+        <v>1.04</v>
       </c>
       <c r="AH13">
-        <v>0.1843434343434344</v>
+        <v>0.1223529411764706</v>
       </c>
       <c r="AI13">
-        <v>0.2683823529411765</v>
+        <v>0.2913165266106443</v>
       </c>
       <c r="AJ13">
-        <v>0.1000278629144608</v>
+        <v>0.1223529411764706</v>
       </c>
       <c r="AK13">
-        <v>0.1528309919114517</v>
+        <v>0.2913165266106443</v>
       </c>
       <c r="AL13">
-        <v>0.108</v>
+        <v>0.054</v>
       </c>
       <c r="AM13">
-        <v>0.09</v>
+        <v>0.054</v>
       </c>
       <c r="AN13">
-        <v>-4.534161490683229</v>
+        <v>-1.672025723472669</v>
       </c>
       <c r="AO13">
-        <v>-15.27777777777778</v>
+        <v>-12</v>
       </c>
       <c r="AP13">
-        <v>-2.229813664596273</v>
+        <v>-1.672025723472669</v>
       </c>
       <c r="AQ13">
-        <v>-18.33333333333333</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="14">
@@ -2127,7 +2106,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LVenture Group S.p.A. (BIT:LVEN)</t>
+          <t>4AIM SICAF S.p.A. (BIT:4AIM)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2135,26 +2114,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D14">
-        <v>0.33</v>
-      </c>
-      <c r="G14">
-        <v>-0.09547325102880658</v>
-      </c>
-      <c r="H14">
-        <v>-0.09547325102880658</v>
-      </c>
-      <c r="I14">
-        <v>-0.5699588477366255</v>
-      </c>
-      <c r="J14">
-        <v>-0.5699588477366255</v>
-      </c>
       <c r="K14">
-        <v>-2.85</v>
-      </c>
-      <c r="L14">
-        <v>-0.5864197530864197</v>
+        <v>-7.05</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2178,73 +2139,67 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>2.39</v>
+        <v>1.54</v>
       </c>
       <c r="V14">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="W14">
-        <v>-0.1091954022988506</v>
+        <v>-0.2231012658227848</v>
       </c>
       <c r="X14">
-        <v>0.06909707490841566</v>
+        <v>0.09404034272219189</v>
       </c>
       <c r="Y14">
-        <v>-0.1782924772072662</v>
+        <v>-0.3171416085449767</v>
       </c>
       <c r="Z14">
-        <v>0.1908127208480566</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>-0.1087553985080487</v>
+        <v>-0.2545774647887324</v>
       </c>
       <c r="AB14">
-        <v>0.06090345387339247</v>
+        <v>0.09404034272219189</v>
       </c>
       <c r="AC14">
-        <v>-0.1696588523814412</v>
+        <v>-0.3486178075109243</v>
       </c>
       <c r="AD14">
-        <v>6.77</v>
+        <v>0</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>6.77</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>4.379999999999999</v>
+        <v>-1.54</v>
       </c>
       <c r="AH14">
-        <v>0.2207368764264754</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>0.2151255163647919</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>0.1548797736916549</v>
+        <v>-0.1235955056179775</v>
       </c>
       <c r="AK14">
-        <v>0.1506189821182943</v>
+        <v>-0.08433734939759036</v>
       </c>
       <c r="AL14">
-        <v>0.179</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>-2.763265306122449</v>
-      </c>
-      <c r="AO14">
-        <v>-15.47486033519553</v>
+        <v>-0</v>
       </c>
       <c r="AP14">
-        <v>-1.787755102040816</v>
-      </c>
-      <c r="AQ14">
-        <v>-16.58682634730539</v>
+        <v>0.2254758418740849</v>
       </c>
     </row>
     <row r="15">
@@ -2264,25 +2219,25 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.5660000000000001</v>
+        <v>0.7809999999999999</v>
       </c>
       <c r="G15">
-        <v>0.005063291139240506</v>
+        <v>-0.5057471264367817</v>
       </c>
       <c r="H15">
-        <v>0.005063291139240506</v>
+        <v>-0.5057471264367817</v>
       </c>
       <c r="I15">
-        <v>-0.1952983725135624</v>
+        <v>-0.5632183908045977</v>
       </c>
       <c r="J15">
-        <v>-0.1952983725135624</v>
+        <v>-0.5632183908045977</v>
       </c>
       <c r="K15">
-        <v>-0.947</v>
+        <v>-3.19</v>
       </c>
       <c r="L15">
-        <v>-0.17124773960217</v>
+        <v>-0.9166666666666666</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2306,73 +2261,73 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>1.17</v>
+        <v>0.313</v>
       </c>
       <c r="V15">
-        <v>0.07358490566037736</v>
+        <v>0.04785932721712538</v>
       </c>
       <c r="W15">
-        <v>-4.190265486725663</v>
+        <v>4.596541786743516</v>
       </c>
       <c r="X15">
-        <v>0.06868529195867561</v>
+        <v>0.1170858704107589</v>
       </c>
       <c r="Y15">
-        <v>-4.258950778684339</v>
+        <v>4.479455916332757</v>
       </c>
       <c r="Z15">
-        <v>3.327316486161252</v>
+        <v>1.422730989370401</v>
       </c>
       <c r="AA15">
-        <v>-0.6498194945848376</v>
+        <v>-0.8013082583810304</v>
       </c>
       <c r="AB15">
-        <v>0.0616054453334267</v>
+        <v>0.09867162588280209</v>
       </c>
       <c r="AC15">
-        <v>-0.7114249399182643</v>
+        <v>-0.8999798842638325</v>
       </c>
       <c r="AD15">
-        <v>4.31</v>
+        <v>3.59</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>4.31</v>
+        <v>3.59</v>
       </c>
       <c r="AG15">
-        <v>3.14</v>
+        <v>3.277</v>
       </c>
       <c r="AH15">
-        <v>0.2132607619990104</v>
+        <v>0.3543928923988154</v>
       </c>
       <c r="AI15">
-        <v>1.191924778761062</v>
+        <v>6.189655172413792</v>
       </c>
       <c r="AJ15">
-        <v>0.1649159663865546</v>
+        <v>0.3338086991952735</v>
       </c>
       <c r="AK15">
-        <v>1.283728536385936</v>
+        <v>12.27340823970038</v>
       </c>
       <c r="AL15">
-        <v>0.151</v>
+        <v>0.244</v>
       </c>
       <c r="AM15">
-        <v>0.151</v>
+        <v>0.244</v>
       </c>
       <c r="AN15">
-        <v>-5.435056746532156</v>
+        <v>-1.869791666666667</v>
       </c>
       <c r="AO15">
-        <v>-7.152317880794703</v>
+        <v>-8.032786885245901</v>
       </c>
       <c r="AP15">
-        <v>-3.959646910466582</v>
+        <v>-1.706770833333333</v>
       </c>
       <c r="AQ15">
-        <v>-7.152317880794703</v>
+        <v>-8.032786885245901</v>
       </c>
     </row>
     <row r="16">
@@ -2383,7 +2338,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H-Farm S.p.A. (BIT:FARM)</t>
+          <t>VAM Investments SPAC B.V. (ENXTAM:VAM)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2391,26 +2346,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D16">
-        <v>0.156</v>
-      </c>
-      <c r="G16">
-        <v>-0.05341426403641882</v>
-      </c>
-      <c r="H16">
-        <v>-0.07268588770864946</v>
-      </c>
-      <c r="I16">
-        <v>-0.1881638846737481</v>
-      </c>
-      <c r="J16">
-        <v>-0.1881638846737481</v>
-      </c>
       <c r="K16">
-        <v>-17.5</v>
-      </c>
-      <c r="L16">
-        <v>-0.2655538694992413</v>
+        <v>-4.78</v>
       </c>
       <c r="M16">
         <v>-0</v>
@@ -2434,177 +2371,52 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>17.5</v>
+        <v>2.58</v>
       </c>
       <c r="V16">
-        <v>0.4807692307692308</v>
-      </c>
-      <c r="W16">
-        <v>-1.411290322580645</v>
+        <v>0.009416058394160584</v>
       </c>
       <c r="X16">
-        <v>0.07929172321987754</v>
-      </c>
-      <c r="Y16">
-        <v>-1.490582045800523</v>
-      </c>
-      <c r="Z16">
-        <v>51.08527131782935</v>
-      </c>
-      <c r="AA16">
-        <v>-9.612403100775174</v>
+        <v>0.09404034272219189</v>
       </c>
       <c r="AB16">
-        <v>0.06312125582358062</v>
-      </c>
-      <c r="AC16">
-        <v>-9.675524356598753</v>
+        <v>0.09404034272219189</v>
       </c>
       <c r="AD16">
-        <v>21.3</v>
+        <v>0</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>21.3</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>3.800000000000001</v>
+        <v>-2.58</v>
       </c>
       <c r="AH16">
-        <v>0.3691507798960139</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>0.726962457337884</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>0.09452736318407962</v>
+        <v>-0.009505563333578954</v>
       </c>
       <c r="AK16">
-        <v>0.3220338983050848</v>
+        <v>4.867924528301884</v>
       </c>
       <c r="AL16">
-        <v>1.44</v>
+        <v>6.11</v>
       </c>
       <c r="AM16">
-        <v>1.44</v>
-      </c>
-      <c r="AN16">
-        <v>-3.307453416149068</v>
+        <v>6.095000000000001</v>
       </c>
       <c r="AO16">
-        <v>-8.611111111111112</v>
-      </c>
-      <c r="AP16">
-        <v>-0.5900621118012424</v>
+        <v>-0.2291325695581014</v>
       </c>
       <c r="AQ16">
-        <v>-8.611111111111112</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Innovative-RFK S.p.A. (ENXTPA:MLIRF)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="G17">
-        <v>-2.229299363057325</v>
-      </c>
-      <c r="H17">
-        <v>-2.229299363057325</v>
-      </c>
-      <c r="I17">
-        <v>-2.261146496815286</v>
-      </c>
-      <c r="J17">
-        <v>-2.261146496815286</v>
-      </c>
-      <c r="K17">
-        <v>-0.336</v>
-      </c>
-      <c r="L17">
-        <v>-2.140127388535032</v>
-      </c>
-      <c r="M17">
-        <v>-0</v>
-      </c>
-      <c r="N17">
-        <v>-0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>-0</v>
-      </c>
-      <c r="Q17">
-        <v>-0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>0.0595317852970933</v>
-      </c>
-      <c r="AB17">
-        <v>0.0595317852970933</v>
-      </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>0</v>
-      </c>
-      <c r="AG17">
-        <v>0</v>
-      </c>
-      <c r="AH17">
-        <v>0</v>
-      </c>
-      <c r="AJ17">
-        <v>0</v>
-      </c>
-      <c r="AL17">
-        <v>0.028</v>
-      </c>
-      <c r="AM17">
-        <v>0.028</v>
-      </c>
-      <c r="AN17">
-        <v>-0</v>
-      </c>
-      <c r="AO17">
-        <v>-12.67857142857143</v>
-      </c>
-      <c r="AP17">
-        <v>-0</v>
-      </c>
-      <c r="AQ17">
-        <v>-12.67857142857143</v>
+        <v>-0.2296964725184577</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/italy/italy_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_investments_asset_management.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0725</v>
+        <v>0.0411</v>
       </c>
       <c r="E2">
-        <v>0.0373</v>
+        <v>0.1365</v>
       </c>
       <c r="F2">
-        <v>-0.01365</v>
+        <v>0.1</v>
       </c>
       <c r="G2">
-        <v>0.379805568975336</v>
+        <v>0.2344424691720908</v>
       </c>
       <c r="H2">
-        <v>0.3795357978000262</v>
+        <v>0.2342092991049096</v>
       </c>
       <c r="I2">
-        <v>0.2844637714874037</v>
+        <v>0.2290128568561892</v>
       </c>
       <c r="J2">
-        <v>0.246276647635102</v>
+        <v>0.2145594328690485</v>
       </c>
       <c r="K2">
-        <v>1031.735</v>
+        <v>928.979</v>
       </c>
       <c r="L2">
-        <v>0.2970462791443561</v>
+        <v>0.2625576919272283</v>
       </c>
       <c r="M2">
-        <v>715.4118000000001</v>
+        <v>621.8220200000001</v>
       </c>
       <c r="N2">
-        <v>0.06832211521932624</v>
+        <v>0.0545305322458014</v>
       </c>
       <c r="O2">
-        <v>0.6934065433468867</v>
+        <v>0.6693606852253926</v>
       </c>
       <c r="P2">
-        <v>595.7318</v>
+        <v>551.97002</v>
       </c>
       <c r="Q2">
-        <v>0.05689262698688589</v>
+        <v>0.04840487793328007</v>
       </c>
       <c r="R2">
-        <v>0.5774077645907137</v>
+        <v>0.59416845805987</v>
       </c>
       <c r="S2">
-        <v>119.68</v>
+        <v>69.852</v>
       </c>
       <c r="T2">
-        <v>0.1672882667017793</v>
+        <v>0.1123343943336069</v>
       </c>
       <c r="U2">
-        <v>1004.869</v>
+        <v>691.98</v>
       </c>
       <c r="V2">
-        <v>0.09596539447396468</v>
+        <v>0.06068301940071155</v>
       </c>
       <c r="W2">
-        <v>0.05359262008768154</v>
+        <v>-0.06699067573892069</v>
       </c>
       <c r="X2">
-        <v>0.1024490019258407</v>
+        <v>0.08322371293069332</v>
       </c>
       <c r="Y2">
-        <v>-0.04885638183815919</v>
+        <v>-0.150214388669614</v>
       </c>
       <c r="Z2">
-        <v>0.4757519262238889</v>
+        <v>0.6253710621457843</v>
       </c>
       <c r="AA2">
-        <v>-0.008930452435252948</v>
+        <v>-0.03378503009927193</v>
       </c>
       <c r="AB2">
-        <v>0.09524628449478098</v>
+        <v>0.07949202784697976</v>
       </c>
       <c r="AC2">
-        <v>-0.1039579625921551</v>
+        <v>-0.1132475524755908</v>
       </c>
       <c r="AD2">
-        <v>3515.879</v>
+        <v>4479.07</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3515.879</v>
+        <v>4479.07</v>
       </c>
       <c r="AG2">
-        <v>2511.01</v>
+        <v>3787.09</v>
       </c>
       <c r="AH2">
-        <v>0.2513669261950295</v>
+        <v>0.2820171688412103</v>
       </c>
       <c r="AI2">
-        <v>0.3939192946316341</v>
+        <v>0.4286700048618209</v>
       </c>
       <c r="AJ2">
-        <v>0.193419898214243</v>
+        <v>0.2493100851333879</v>
       </c>
       <c r="AK2">
-        <v>0.3170263025992013</v>
+        <v>0.388149573937303</v>
       </c>
       <c r="AL2">
-        <v>46.309</v>
+        <v>142.861</v>
       </c>
       <c r="AM2">
-        <v>30.396</v>
+        <v>135.614</v>
       </c>
       <c r="AN2">
-        <v>3.308187669896244</v>
+        <v>4.943605806852509</v>
       </c>
       <c r="AO2">
-        <v>21.33563670128917</v>
+        <v>5.671883859135805</v>
       </c>
       <c r="AP2">
-        <v>2.362678670393994</v>
+        <v>4.179858791015338</v>
       </c>
       <c r="AQ2">
-        <v>32.50532964863798</v>
+        <v>5.974980459244622</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Innovative-RFK S.p.A. (ENXTPA:MLIRF)</t>
+          <t>Azimut Holding S.p.A. (BIT:AZM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,101 +724,125 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.112</v>
+      </c>
+      <c r="E3">
+        <v>0.199</v>
+      </c>
+      <c r="F3">
+        <v>0.08210000000000001</v>
+      </c>
       <c r="G3">
-        <v>-3.929824561403509</v>
+        <v>0.3823782587309394</v>
       </c>
       <c r="H3">
-        <v>-3.929824561403509</v>
+        <v>0.3823782587309394</v>
       </c>
       <c r="I3">
-        <v>25.70175438596491</v>
+        <v>0.389264633546483</v>
       </c>
       <c r="J3">
-        <v>25.70175438596491</v>
+        <v>0.2932242990654205</v>
       </c>
       <c r="K3">
-        <v>2.96</v>
+        <v>446.6</v>
       </c>
       <c r="L3">
-        <v>25.96491228070175</v>
+        <v>0.2745941957697983</v>
       </c>
       <c r="M3">
-        <v>8.98</v>
+        <v>261.69</v>
       </c>
       <c r="N3">
-        <v>0.4961325966850829</v>
+        <v>0.0723700221238938</v>
       </c>
       <c r="O3">
-        <v>3.033783783783784</v>
+        <v>0.5859605911330049</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>253.2</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.07002212389380531</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.566950291088222</v>
       </c>
       <c r="S3">
-        <v>8.98</v>
+        <v>8.490000000000009</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0.03244296686919641</v>
       </c>
       <c r="U3">
-        <v>7.52</v>
+        <v>471.6</v>
       </c>
       <c r="V3">
-        <v>0.4154696132596685</v>
+        <v>0.1304203539823009</v>
+      </c>
+      <c r="W3">
+        <v>0.3470085470085471</v>
       </c>
       <c r="X3">
-        <v>0.102390485135889</v>
+        <v>0.08320428313974856</v>
+      </c>
+      <c r="Y3">
+        <v>0.2638042638687985</v>
+      </c>
+      <c r="Z3">
+        <v>1.931591448931117</v>
+      </c>
+      <c r="AA3">
+        <v>0.5663895486935868</v>
       </c>
       <c r="AB3">
-        <v>0.09620834182750405</v>
+        <v>0.07925480351618076</v>
+      </c>
+      <c r="AC3">
+        <v>0.4871347451774061</v>
       </c>
       <c r="AD3">
-        <v>3.6</v>
+        <v>532.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.6</v>
+        <v>532.4</v>
       </c>
       <c r="AG3">
-        <v>-3.919999999999999</v>
+        <v>60.79999999999995</v>
       </c>
       <c r="AH3">
-        <v>0.1658986175115207</v>
+        <v>0.1283386365827789</v>
       </c>
       <c r="AI3">
-        <v>0.2105263157894737</v>
+        <v>0.2314983911644491</v>
       </c>
       <c r="AJ3">
-        <v>-0.2764456981664316</v>
+        <v>0.01653611836379459</v>
       </c>
       <c r="AK3">
-        <v>-0.4091858037578288</v>
+        <v>0.0332567552784159</v>
       </c>
       <c r="AL3">
-        <v>0.102</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AM3">
-        <v>0.102</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AN3">
-        <v>1.228668941979522</v>
+        <v>0.7828260549919129</v>
       </c>
       <c r="AO3">
-        <v>28.72549019607844</v>
+        <v>69.26695842450766</v>
       </c>
       <c r="AP3">
-        <v>-1.337883959044368</v>
+        <v>0.08939861785031605</v>
       </c>
       <c r="AQ3">
-        <v>28.72549019607844</v>
+        <v>69.26695842450766</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Azimut Holding S.p.A. (BIT:AZM)</t>
+          <t>Anima Holding SpA (BIT:ANIM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,124 +862,124 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.131</v>
+        <v>-0.0139</v>
       </c>
       <c r="E4">
-        <v>0.23</v>
+        <v>0.00026</v>
       </c>
       <c r="F4">
-        <v>-0.058</v>
+        <v>0.1</v>
       </c>
       <c r="G4">
-        <v>0.4927887388946579</v>
+        <v>0.2590131900341964</v>
       </c>
       <c r="H4">
-        <v>0.4927887388946579</v>
+        <v>0.2590131900341964</v>
       </c>
       <c r="I4">
-        <v>0.4485404407522787</v>
+        <v>0.2201270151441133</v>
       </c>
       <c r="J4">
-        <v>0.3371254378734055</v>
+        <v>0.1486502255587445</v>
       </c>
       <c r="K4">
-        <v>573.9</v>
+        <v>138.1</v>
       </c>
       <c r="L4">
-        <v>0.3310834198684666</v>
+        <v>0.1349291646311676</v>
       </c>
       <c r="M4">
-        <v>275.08</v>
+        <v>136.6</v>
       </c>
       <c r="N4">
-        <v>0.08841320348407419</v>
+        <v>0.09750874437861373</v>
       </c>
       <c r="O4">
-        <v>0.479316954173201</v>
+        <v>0.9891383055756698</v>
       </c>
       <c r="P4">
-        <v>267.6</v>
+        <v>75.5</v>
       </c>
       <c r="Q4">
-        <v>0.08600906373541607</v>
+        <v>0.05389392533371404</v>
       </c>
       <c r="R4">
-        <v>0.4662833246210142</v>
+        <v>0.5467052860246199</v>
       </c>
       <c r="S4">
-        <v>7.480000000000018</v>
+        <v>61.09999999999999</v>
       </c>
       <c r="T4">
-        <v>0.02719208957394219</v>
+        <v>0.4472913616398243</v>
       </c>
       <c r="U4">
-        <v>312.1</v>
+        <v>182.1</v>
       </c>
       <c r="V4">
-        <v>0.100311766785588</v>
+        <v>0.1299878649439646</v>
       </c>
       <c r="W4">
-        <v>0.5463112803426939</v>
+        <v>0.1018887413309724</v>
       </c>
       <c r="X4">
-        <v>0.1019395004499822</v>
+        <v>0.09295238558134192</v>
       </c>
       <c r="Y4">
-        <v>0.4443717798927117</v>
+        <v>0.008936355749630476</v>
       </c>
       <c r="Z4">
-        <v>1.223658239750609</v>
+        <v>2.439809296781882</v>
       </c>
       <c r="AA4">
-        <v>0.4125263198833247</v>
+        <v>0.3626782022869486</v>
       </c>
       <c r="AB4">
-        <v>0.09472574811939445</v>
+        <v>0.08002616216286272</v>
       </c>
       <c r="AC4">
-        <v>0.3178005717639303</v>
+        <v>0.2826520401240858</v>
       </c>
       <c r="AD4">
-        <v>585.4</v>
+        <v>656.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>585.4</v>
+        <v>656.2</v>
       </c>
       <c r="AG4">
-        <v>273.3</v>
+        <v>474.1</v>
       </c>
       <c r="AH4">
-        <v>0.1583574539454108</v>
+        <v>0.3189927567935443</v>
       </c>
       <c r="AI4">
-        <v>0.3044043471478342</v>
+        <v>0.3078872049922582</v>
       </c>
       <c r="AJ4">
-        <v>0.08074809430951957</v>
+        <v>0.2528533333333333</v>
       </c>
       <c r="AK4">
-        <v>0.1696461824953445</v>
+        <v>0.2432279909706547</v>
       </c>
       <c r="AL4">
-        <v>12.2</v>
+        <v>13.4</v>
       </c>
       <c r="AM4">
-        <v>12.2</v>
+        <v>13.4</v>
       </c>
       <c r="AN4">
-        <v>0.7248637939574046</v>
+        <v>2.443947858472998</v>
       </c>
       <c r="AO4">
-        <v>63.72950819672131</v>
+        <v>16.8134328358209</v>
       </c>
       <c r="AP4">
-        <v>0.338410104011887</v>
+        <v>1.765735567970205</v>
       </c>
       <c r="AQ4">
-        <v>63.72950819672131</v>
+        <v>16.8134328358209</v>
       </c>
     </row>
     <row r="5">
@@ -966,7 +990,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A. (BIT:ANIM)</t>
+          <t>First Capital S.p.A. (BIT:FIC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -975,121 +999,118 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0736</v>
-      </c>
-      <c r="E5">
-        <v>0.0508</v>
+        <v>-0.187</v>
       </c>
       <c r="G5">
-        <v>0.4052402555318952</v>
+        <v>-3.69626168224299</v>
       </c>
       <c r="H5">
-        <v>0.4052402555318952</v>
+        <v>-3.69626168224299</v>
       </c>
       <c r="I5">
-        <v>0.2311822979353764</v>
+        <v>0.1906542056074766</v>
       </c>
       <c r="J5">
-        <v>0.1525197266089695</v>
+        <v>0.1906542056074766</v>
       </c>
       <c r="K5">
-        <v>146</v>
+        <v>-1.56</v>
       </c>
       <c r="L5">
-        <v>0.1351726691972966</v>
+        <v>-0.7289719626168224</v>
       </c>
       <c r="M5">
-        <v>196.3</v>
+        <v>1.07342</v>
       </c>
       <c r="N5">
-        <v>0.1500879272115605</v>
+        <v>0.01930611510791367</v>
       </c>
       <c r="O5">
-        <v>1.344520547945206</v>
+        <v>-0.6880897435897436</v>
       </c>
       <c r="P5">
-        <v>93.3</v>
+        <v>1.07342</v>
       </c>
       <c r="Q5">
-        <v>0.0713357290312715</v>
+        <v>0.01930611510791367</v>
       </c>
       <c r="R5">
-        <v>0.6390410958904109</v>
+        <v>-0.6880897435897436</v>
       </c>
       <c r="S5">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.5247070809984717</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>540.8</v>
+        <v>10.5</v>
       </c>
       <c r="V5">
-        <v>0.4134872696689349</v>
+        <v>0.1888489208633093</v>
       </c>
       <c r="W5">
-        <v>0.08913853104585139</v>
+        <v>-0.01979695431472081</v>
       </c>
       <c r="X5">
-        <v>0.1161535431174833</v>
+        <v>0.09800519217628739</v>
       </c>
       <c r="Y5">
-        <v>-0.02701501207163194</v>
+        <v>-0.1178021464910082</v>
       </c>
       <c r="Z5">
-        <v>0.8686008939327408</v>
+        <v>0.01859091303970116</v>
       </c>
       <c r="AA5">
-        <v>0.1324787708749281</v>
+        <v>0.003544435757101902</v>
       </c>
       <c r="AB5">
-        <v>0.09553358619858679</v>
+        <v>0.08030672623416414</v>
       </c>
       <c r="AC5">
-        <v>0.03694518467634134</v>
+        <v>-0.07676229047706223</v>
       </c>
       <c r="AD5">
-        <v>688.9</v>
+        <v>35.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>688.9</v>
+        <v>35.3</v>
       </c>
       <c r="AG5">
-        <v>148.1</v>
+        <v>24.8</v>
       </c>
       <c r="AH5">
-        <v>0.3450020032051281</v>
+        <v>0.3883388338833883</v>
       </c>
       <c r="AI5">
-        <v>0.3369857652986352</v>
+        <v>0.2951505016722408</v>
       </c>
       <c r="AJ5">
-        <v>0.101717032967033</v>
+        <v>0.308457711442786</v>
       </c>
       <c r="AK5">
-        <v>0.09850349185234454</v>
+        <v>0.227314390467461</v>
       </c>
       <c r="AL5">
-        <v>12.5</v>
+        <v>1.83</v>
       </c>
       <c r="AM5">
-        <v>12.5</v>
+        <v>1.83</v>
       </c>
       <c r="AN5">
-        <v>2.376336667816489</v>
+        <v>84.44976076555024</v>
       </c>
       <c r="AO5">
-        <v>19.976</v>
+        <v>0.2229508196721311</v>
       </c>
       <c r="AP5">
-        <v>0.5108658157985514</v>
+        <v>59.33014354066985</v>
       </c>
       <c r="AQ5">
-        <v>19.976</v>
+        <v>0.2229508196721311</v>
       </c>
     </row>
     <row r="6">
@@ -1100,7 +1121,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LVenture Group S.p.A. (BIT:LVEN)</t>
+          <t>Banca Generali S.p.A. (BIT:BGN)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1109,115 +1130,112 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.375</v>
+        <v>0.09609999999999999</v>
+      </c>
+      <c r="E6">
+        <v>0.102</v>
+      </c>
+      <c r="F6">
+        <v>0.148</v>
       </c>
       <c r="G6">
-        <v>0.2281553398058252</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>0.2281553398058252</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0.270873786407767</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0.270873786407767</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>2.67</v>
+        <v>331</v>
       </c>
       <c r="L6">
-        <v>0.2592233009708738</v>
+        <v>0.4070839995080556</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>199.325</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.04705167245001535</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.6021903323262841</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>199.325</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.04705167245001535</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.6021903323262841</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>0.1058252427184466</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>0.1080971659919028</v>
+        <v>0.3323293172690763</v>
       </c>
       <c r="X6">
-        <v>0.1067370405241838</v>
+        <v>0.09778528928758834</v>
       </c>
       <c r="Y6">
-        <v>0.001360125467718992</v>
+        <v>0.234544027981488</v>
       </c>
       <c r="Z6">
-        <v>0.3510565780504431</v>
+        <v>0.2974574721053594</v>
       </c>
       <c r="AA6">
-        <v>0.09509202453987731</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.09504536660762546</v>
+        <v>0.08029571037377523</v>
       </c>
       <c r="AC6">
-        <v>4.665793225185066e-05</v>
+        <v>-0.08029571037377523</v>
       </c>
       <c r="AD6">
-        <v>6.23</v>
+        <v>2658.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>6.23</v>
+        <v>2658.9</v>
       </c>
       <c r="AG6">
-        <v>4.050000000000001</v>
+        <v>2658.9</v>
       </c>
       <c r="AH6">
-        <v>0.2322027581065971</v>
+        <v>0.3856160807518274</v>
       </c>
       <c r="AI6">
-        <v>0.1763373903198415</v>
+        <v>0.6889591376674526</v>
       </c>
       <c r="AJ6">
-        <v>0.1643002028397566</v>
+        <v>0.3856160807518274</v>
       </c>
       <c r="AK6">
-        <v>0.1221719457013575</v>
+        <v>0.6889591376674526</v>
       </c>
       <c r="AL6">
-        <v>0.155</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="AN6">
-        <v>2.076666666666667</v>
-      </c>
-      <c r="AO6">
-        <v>18</v>
-      </c>
-      <c r="AP6">
-        <v>1.35</v>
-      </c>
-      <c r="AQ6">
-        <v>32.06896551724138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1228,7 +1246,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A. (BIT:BGN)</t>
+          <t>Ambromobiliare S.p.A. (BIT:AMB)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1237,13 +1255,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.07139999999999999</v>
-      </c>
-      <c r="E7">
-        <v>0.0238</v>
-      </c>
-      <c r="F7">
-        <v>0.0307</v>
+        <v>-0.131</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1258,85 +1270,82 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>203.6</v>
+        <v>-0.483</v>
       </c>
       <c r="L7">
-        <v>0.3635714285714285</v>
+        <v>-0.3425531914893617</v>
       </c>
       <c r="M7">
-        <v>216.785</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.05574168830834898</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>1.064759332023576</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>216.785</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.05574168830834898</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>1.064759332023576</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>0.07416879795396418</v>
       </c>
       <c r="W7">
-        <v>0.1680422581710135</v>
+        <v>-0.1141843971631206</v>
       </c>
       <c r="X7">
-        <v>0.112796577471788</v>
+        <v>0.08573725932059953</v>
       </c>
       <c r="Y7">
-        <v>0.05524568069922549</v>
+        <v>-0.1999216564837201</v>
       </c>
       <c r="Z7">
-        <v>0.2347811504276371</v>
+        <v>0.6549001393404549</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.09537690063297448</v>
+        <v>0.08032193204697194</v>
       </c>
       <c r="AC7">
-        <v>-0.09537690063297448</v>
+        <v>-0.08032193204697194</v>
       </c>
       <c r="AD7">
-        <v>1737.5</v>
+        <v>0.902</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1737.5</v>
+        <v>0.902</v>
       </c>
       <c r="AG7">
-        <v>1737.5</v>
+        <v>0.6120000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.3088010521451676</v>
+        <v>0.1874480465502909</v>
       </c>
       <c r="AI7">
-        <v>0.6355157278712509</v>
+        <v>0.1862866584056175</v>
       </c>
       <c r="AJ7">
-        <v>0.3088010521451676</v>
+        <v>0.1353383458646617</v>
       </c>
       <c r="AK7">
-        <v>0.6355157278712509</v>
+        <v>0.1344463971880492</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1353,7 +1362,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A. (BIT:AMB)</t>
+          <t>Copernico Sim S.p.A. (BIT:COP)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1361,107 +1370,116 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D8">
-        <v>0.00465</v>
-      </c>
-      <c r="E8">
-        <v>-0.216</v>
-      </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.04513172966781214</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.03459335624284077</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>-0.006071019473081328</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>-0.006071019473081328</v>
       </c>
       <c r="K8">
-        <v>0.08500000000000001</v>
+        <v>-0.068</v>
       </c>
       <c r="L8">
-        <v>0.02871621621621622</v>
+        <v>-0.007789232531500573</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>0.005</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.0006150061500615005</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>-0.07352941176470588</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>0.005</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.0006150061500615005</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>-0.07352941176470588</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>0.516</v>
+        <v>1.05</v>
       </c>
       <c r="V8">
-        <v>0.1240384615384615</v>
+        <v>0.1291512915129151</v>
       </c>
       <c r="W8">
-        <v>0.01804670912951168</v>
+        <v>-0.01468682505399568</v>
       </c>
       <c r="X8">
-        <v>0.1025075187157925</v>
+        <v>0.07988166084824859</v>
       </c>
       <c r="Y8">
-        <v>-0.0844608095862808</v>
+        <v>-0.09456848590224427</v>
       </c>
       <c r="Z8">
-        <v>1.297107800175285</v>
+        <v>2.259901630856847</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>-0.01371990680818017</v>
       </c>
       <c r="AB8">
-        <v>0.09574892482255891</v>
+        <v>0.07888278204358511</v>
       </c>
       <c r="AC8">
-        <v>-0.09574892482255891</v>
+        <v>-0.09260268885176527</v>
       </c>
       <c r="AD8">
-        <v>0.839</v>
+        <v>0.307</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0.839</v>
+        <v>0.307</v>
       </c>
       <c r="AG8">
-        <v>0.323</v>
+        <v>-0.7430000000000001</v>
       </c>
       <c r="AH8">
-        <v>0.1678335667133427</v>
+        <v>0.03638734147208723</v>
       </c>
       <c r="AI8">
-        <v>0.165515880844348</v>
+        <v>0.05817699450445329</v>
       </c>
       <c r="AJ8">
-        <v>0.0720499665402632</v>
+        <v>-0.1005821036956816</v>
       </c>
       <c r="AK8">
-        <v>0.07094223588842519</v>
+        <v>-0.1757747811686776</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="AN8">
+        <v>2.033112582781457</v>
+      </c>
+      <c r="AO8">
+        <v>-5.3</v>
+      </c>
+      <c r="AP8">
+        <v>-4.920529801324504</v>
+      </c>
+      <c r="AQ8">
+        <v>-5.3</v>
       </c>
     </row>
     <row r="9">
@@ -1472,7 +1490,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DeA Capital S.p.A. (BIT:DEA)</t>
+          <t>Tamburi Investment Partners S.p.A. (BIT:TIP)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1481,118 +1499,121 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.0132</v>
+        <v>-0.214</v>
       </c>
       <c r="E9">
-        <v>-0.42</v>
+        <v>0.171</v>
       </c>
       <c r="G9">
-        <v>0.6402877697841727</v>
+        <v>-19.04494382022472</v>
       </c>
       <c r="H9">
-        <v>0.6402877697841727</v>
+        <v>-19.04494382022472</v>
       </c>
       <c r="I9">
-        <v>-0.0223021582733813</v>
+        <v>-15.0561797752809</v>
       </c>
       <c r="J9">
-        <v>-0.01115107913669065</v>
+        <v>-15.0561797752809</v>
       </c>
       <c r="K9">
-        <v>0.483</v>
+        <v>47.9</v>
       </c>
       <c r="L9">
-        <v>0.006949640287769784</v>
+        <v>26.91011235955056</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>22.8666</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.01342724603640634</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0.4773820459290188</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>22.8666</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.01342724603640634</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.4773820459290188</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>86.5</v>
+        <v>6.76</v>
       </c>
       <c r="V9">
-        <v>0.2064439140811456</v>
+        <v>0.003969465648854962</v>
       </c>
       <c r="W9">
-        <v>0.0009415204678362573</v>
+        <v>0.04439295644114921</v>
       </c>
       <c r="X9">
-        <v>0.09508239443788688</v>
+        <v>0.08913832138325123</v>
       </c>
       <c r="Y9">
-        <v>-0.09414087397005062</v>
+        <v>-0.04474536494210202</v>
       </c>
       <c r="Z9">
-        <v>0.2634571645185746</v>
+        <v>0.001214287663383087</v>
       </c>
       <c r="AA9">
-        <v>-0.002937831690674754</v>
+        <v>-0.01828253335880154</v>
       </c>
       <c r="AB9">
-        <v>0.09414517144837756</v>
+        <v>0.07976830338113458</v>
       </c>
       <c r="AC9">
-        <v>-0.09708300313905231</v>
+        <v>-0.09805083673993611</v>
       </c>
       <c r="AD9">
-        <v>10.4</v>
+        <v>583.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>10.4</v>
+        <v>583.7</v>
       </c>
       <c r="AG9">
-        <v>-76.09999999999999</v>
+        <v>576.9400000000001</v>
       </c>
       <c r="AH9">
-        <v>0.02421984163949698</v>
+        <v>0.2552586696986925</v>
       </c>
       <c r="AI9">
-        <v>0.02395209580838323</v>
+        <v>0.2993947476405416</v>
       </c>
       <c r="AJ9">
-        <v>-0.2219305920093322</v>
+        <v>0.2530505188733037</v>
       </c>
       <c r="AK9">
-        <v>-0.2188668392292205</v>
+        <v>0.2969570319738115</v>
       </c>
       <c r="AL9">
-        <v>0.285</v>
+        <v>106.7</v>
       </c>
       <c r="AM9">
-        <v>-0.207</v>
+        <v>106.7</v>
       </c>
       <c r="AN9">
-        <v>15.45319465081724</v>
+        <v>-21.86142322097378</v>
       </c>
       <c r="AO9">
-        <v>-5.438596491228071</v>
+        <v>-0.2511715089034677</v>
       </c>
       <c r="AP9">
-        <v>-113.075780089153</v>
+        <v>-21.60823970037453</v>
       </c>
       <c r="AQ9">
-        <v>7.487922705314009</v>
+        <v>-0.2511715089034677</v>
       </c>
     </row>
     <row r="10">
@@ -1603,7 +1624,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>First Capital S.p.A. (BIT:FIC)</t>
+          <t>Digital Magics S.p.A. (BIT:DM)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1611,17 +1632,35 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D10">
+        <v>0.136</v>
+      </c>
+      <c r="G10">
+        <v>0.05017421602787457</v>
+      </c>
+      <c r="H10">
+        <v>-0.06742160278745644</v>
+      </c>
+      <c r="I10">
+        <v>-0.1759581881533101</v>
+      </c>
+      <c r="J10">
+        <v>-0.1759581881533101</v>
+      </c>
       <c r="K10">
-        <v>-4.41</v>
+        <v>-4.2</v>
+      </c>
+      <c r="L10">
+        <v>-0.7317073170731707</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>0.262</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.009225352112676057</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>-0.06238095238095238</v>
       </c>
       <c r="P10">
         <v>-0</v>
@@ -1633,76 +1672,79 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>0.262</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
       </c>
       <c r="U10">
-        <v>5.99</v>
+        <v>5.51</v>
       </c>
       <c r="V10">
-        <v>0.1079279279279279</v>
+        <v>0.1940140845070422</v>
       </c>
       <c r="W10">
-        <v>-0.0504</v>
+        <v>-0.1578947368421053</v>
       </c>
       <c r="X10">
-        <v>0.1259622935651854</v>
+        <v>0.08226226823820841</v>
       </c>
       <c r="Y10">
-        <v>-0.1763622935651854</v>
+        <v>-0.2401570050803137</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>0.2801093109506148</v>
       </c>
       <c r="AA10">
-        <v>-0.01492307317983114</v>
+        <v>-0.04928752683974233</v>
       </c>
       <c r="AB10">
-        <v>0.09590984886542675</v>
+        <v>0.07915674137150311</v>
       </c>
       <c r="AC10">
-        <v>-0.1108329220452579</v>
+        <v>-0.1284442682112454</v>
       </c>
       <c r="AD10">
-        <v>42.2</v>
+        <v>3.3</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>42.2</v>
+        <v>3.3</v>
       </c>
       <c r="AG10">
-        <v>36.21</v>
+        <v>-2.21</v>
       </c>
       <c r="AH10">
-        <v>0.4319344933469806</v>
+        <v>0.1041009463722397</v>
       </c>
       <c r="AI10">
-        <v>0.3403225806451613</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="AJ10">
-        <v>0.3948315341838403</v>
+        <v>-0.08438335242458954</v>
       </c>
       <c r="AK10">
-        <v>0.306838403525125</v>
+        <v>-0.1042944785276074</v>
       </c>
       <c r="AL10">
-        <v>3.16</v>
+        <v>0.078</v>
       </c>
       <c r="AM10">
-        <v>3.16</v>
+        <v>0.055</v>
       </c>
       <c r="AN10">
-        <v>-23.18681318681319</v>
+        <v>-3.142857142857142</v>
       </c>
       <c r="AO10">
-        <v>-0.5822784810126582</v>
+        <v>-12.94871794871795</v>
       </c>
       <c r="AP10">
-        <v>-19.89560439560439</v>
+        <v>2.104761904761905</v>
       </c>
       <c r="AQ10">
-        <v>-0.5822784810126582</v>
+        <v>-18.36363636363636</v>
       </c>
     </row>
     <row r="11">
@@ -1713,7 +1755,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tamburi Investment Partners S.p.A. (BIT:TIP)</t>
+          <t>Solutions Capital Management SIM S.p.A. (BIT:SCM)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1722,121 +1764,115 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.141</v>
-      </c>
-      <c r="E11">
-        <v>0.156</v>
+        <v>-0.0148</v>
       </c>
       <c r="G11">
-        <v>-16.43292682926829</v>
+        <v>-0.07537688442211055</v>
       </c>
       <c r="H11">
-        <v>-16.43292682926829</v>
+        <v>-0.08266331658291458</v>
       </c>
       <c r="I11">
-        <v>-8.871951219512196</v>
+        <v>-0.04195979899497488</v>
       </c>
       <c r="J11">
-        <v>-8.871951219512196</v>
+        <v>-0.04195979899497488</v>
       </c>
       <c r="K11">
-        <v>123.9</v>
+        <v>-0.5</v>
       </c>
       <c r="L11">
-        <v>37.77439024390245</v>
+        <v>-0.06281407035175879</v>
       </c>
       <c r="M11">
-        <v>18.0468</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.01382578717536198</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>0.1456561743341404</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>18.0468</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.01382578717536198</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.1456561743341404</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>35</v>
+        <v>0.925</v>
       </c>
       <c r="V11">
-        <v>0.02681375928905233</v>
+        <v>0.1178343949044586</v>
       </c>
       <c r="W11">
-        <v>0.0989142583426473</v>
+        <v>-0.1976284584980237</v>
       </c>
       <c r="X11">
-        <v>0.1079187752605475</v>
+        <v>0.08194852023006527</v>
       </c>
       <c r="Y11">
-        <v>-0.009004516917900218</v>
+        <v>-0.279576978728089</v>
       </c>
       <c r="Z11">
-        <v>0.0018433904896787</v>
+        <v>2.2296918767507</v>
       </c>
       <c r="AA11">
-        <v>-0.01635447050294212</v>
+        <v>-0.09355742296918769</v>
       </c>
       <c r="AB11">
-        <v>0.09511566835658747</v>
+        <v>0.07912285877405277</v>
       </c>
       <c r="AC11">
-        <v>-0.1114701388595296</v>
+        <v>-0.1726802817432405</v>
       </c>
       <c r="AD11">
-        <v>431.5</v>
+        <v>0.831</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>431.5</v>
+        <v>0.831</v>
       </c>
       <c r="AG11">
-        <v>396.5</v>
+        <v>-0.09400000000000008</v>
       </c>
       <c r="AH11">
-        <v>0.2484454168585905</v>
+        <v>0.09572629881350075</v>
       </c>
       <c r="AI11">
-        <v>0.278207607994842</v>
+        <v>0.214120072146354</v>
       </c>
       <c r="AJ11">
-        <v>0.2329886003055588</v>
+        <v>-0.01211964930376484</v>
       </c>
       <c r="AK11">
-        <v>0.2615435356200528</v>
+        <v>-0.03179972936400545</v>
       </c>
       <c r="AL11">
-        <v>11.4</v>
+        <v>0.046</v>
       </c>
       <c r="AM11">
-        <v>-3.9</v>
+        <v>0.046</v>
       </c>
       <c r="AN11">
-        <v>-14.87931034482759</v>
+        <v>-2.549079754601227</v>
       </c>
       <c r="AO11">
-        <v>-2.552631578947369</v>
+        <v>-7.260869565217392</v>
       </c>
       <c r="AP11">
-        <v>-13.67241379310345</v>
+        <v>0.2883435582822088</v>
       </c>
       <c r="AQ11">
-        <v>7.461538461538461</v>
+        <v>-7.260869565217392</v>
       </c>
     </row>
     <row r="12">
@@ -1847,7 +1883,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Digital Magics S.p.A. (BIT:DM)</t>
+          <t>LVenture Group S.p.A. (BIT:LVEN)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1856,34 +1892,34 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.104</v>
+        <v>0.156</v>
       </c>
       <c r="G12">
-        <v>-0.1744525547445256</v>
+        <v>-0.5956937799043063</v>
       </c>
       <c r="H12">
-        <v>-0.3941605839416059</v>
+        <v>-0.5956937799043063</v>
       </c>
       <c r="I12">
-        <v>-0.2822384428223844</v>
+        <v>-1</v>
       </c>
       <c r="J12">
-        <v>-0.2822384428223844</v>
+        <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1.67</v>
+        <v>-4.47</v>
       </c>
       <c r="L12">
-        <v>-0.4063260340632603</v>
+        <v>-1.069377990430622</v>
       </c>
       <c r="M12">
-        <v>0.22</v>
+        <v>-0</v>
       </c>
       <c r="N12">
-        <v>0.005759162303664921</v>
+        <v>-0</v>
       </c>
       <c r="O12">
-        <v>-0.1317365269461078</v>
+        <v>0</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1895,79 +1931,76 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <v>0.22</v>
-      </c>
-      <c r="T12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>9.83</v>
+        <v>0.236</v>
       </c>
       <c r="V12">
-        <v>0.2573298429319372</v>
+        <v>0.01340909090909091</v>
       </c>
       <c r="W12">
-        <v>-0.08391959798994975</v>
+        <v>-0.1536082474226804</v>
       </c>
       <c r="X12">
-        <v>0.09918376814089064</v>
+        <v>0.08861689344686538</v>
       </c>
       <c r="Y12">
-        <v>-0.1831033661308404</v>
+        <v>-0.2422251408695458</v>
       </c>
       <c r="Z12">
-        <v>0.1843049327354261</v>
+        <v>0.1260935143288084</v>
       </c>
       <c r="AA12">
-        <v>-0.05201793721973094</v>
+        <v>-0.1260935143288084</v>
       </c>
       <c r="AB12">
-        <v>0.0945127320589656</v>
+        <v>0.07972925217777874</v>
       </c>
       <c r="AC12">
-        <v>-0.1465306692786965</v>
+        <v>-0.2058227665065872</v>
       </c>
       <c r="AD12">
-        <v>4.68</v>
+        <v>5.73</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>4.68</v>
+        <v>5.73</v>
       </c>
       <c r="AG12">
-        <v>-5.15</v>
+        <v>5.494000000000001</v>
       </c>
       <c r="AH12">
-        <v>0.1091417910447761</v>
+        <v>0.2456065152164595</v>
       </c>
       <c r="AI12">
-        <v>0.149616368286445</v>
+        <v>0.1805861960289946</v>
       </c>
       <c r="AJ12">
-        <v>-0.1558245083207262</v>
+        <v>0.2378972893392223</v>
       </c>
       <c r="AK12">
-        <v>-0.2400932400932401</v>
+        <v>0.1744459262081667</v>
       </c>
       <c r="AL12">
-        <v>0.099</v>
+        <v>0.092</v>
       </c>
       <c r="AM12">
-        <v>0.06100000000000001</v>
+        <v>0.092</v>
       </c>
       <c r="AN12">
-        <v>-4.141592920353983</v>
+        <v>-1.425373134328358</v>
       </c>
       <c r="AO12">
-        <v>-11.71717171717172</v>
+        <v>-45.43478260869565</v>
       </c>
       <c r="AP12">
-        <v>4.557522123893806</v>
+        <v>-1.366666666666667</v>
       </c>
       <c r="AQ12">
-        <v>-19.01639344262295</v>
+        <v>-45.43478260869565</v>
       </c>
     </row>
     <row r="13">
@@ -1978,7 +2011,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Solutions Capital Management SIM S.p.A. (BIT:SCM)</t>
+          <t>4AIM SICAF S.p.A. (BIT:AIM)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1986,26 +2019,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D13">
-        <v>-0.0578</v>
-      </c>
-      <c r="G13">
-        <v>-0.01663920922570017</v>
-      </c>
-      <c r="H13">
-        <v>-0.02224052718286656</v>
-      </c>
-      <c r="I13">
-        <v>-0.1067545304777595</v>
-      </c>
-      <c r="J13">
-        <v>-0.1067545304777595</v>
-      </c>
       <c r="K13">
-        <v>-0.763</v>
-      </c>
-      <c r="L13">
-        <v>-0.1257001647446458</v>
+        <v>-2.97</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -2029,73 +2044,73 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>0.09411764705882354</v>
       </c>
       <c r="W13">
-        <v>-0.2051075268817204</v>
+        <v>-0.15</v>
       </c>
       <c r="X13">
-        <v>0.09989315329693996</v>
+        <v>0.07873556418937229</v>
       </c>
       <c r="Y13">
-        <v>-0.3050006801786604</v>
+        <v>-0.2287355641893723</v>
       </c>
       <c r="Z13">
-        <v>1.438388625592417</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>-0.1535545023696682</v>
+        <v>-0.1653888280394304</v>
       </c>
       <c r="AB13">
-        <v>0.09563927748718161</v>
+        <v>0.07873556418937229</v>
       </c>
       <c r="AC13">
-        <v>-0.2491937798568498</v>
+        <v>-0.2441243922288027</v>
       </c>
       <c r="AD13">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>1.04</v>
+        <v>-1.12</v>
       </c>
       <c r="AH13">
-        <v>0.1223529411764706</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>0.2913165266106443</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
-        <v>0.1223529411764706</v>
+        <v>-0.1038961038961039</v>
       </c>
       <c r="AK13">
-        <v>0.2913165266106443</v>
+        <v>-0.06444188722669736</v>
       </c>
       <c r="AL13">
-        <v>0.054</v>
+        <v>0.002</v>
       </c>
       <c r="AM13">
-        <v>0.054</v>
+        <v>-0.162</v>
       </c>
       <c r="AN13">
-        <v>-1.672025723472669</v>
+        <v>-0</v>
       </c>
       <c r="AO13">
-        <v>-12</v>
+        <v>-1510</v>
       </c>
       <c r="AP13">
-        <v>-1.672025723472669</v>
+        <v>0.4179104477611941</v>
       </c>
       <c r="AQ13">
-        <v>-12</v>
+        <v>18.64197530864197</v>
       </c>
     </row>
     <row r="14">
@@ -2106,7 +2121,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4AIM SICAF S.p.A. (BIT:4AIM)</t>
+          <t>Bestbe Holding S.p.A. (BIT:BES)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2114,8 +2129,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D14">
+        <v>0.611</v>
+      </c>
+      <c r="G14">
+        <v>-0.3614457831325301</v>
+      </c>
+      <c r="H14">
+        <v>-0.3614457831325301</v>
+      </c>
+      <c r="I14">
+        <v>-0.3373493975903614</v>
+      </c>
+      <c r="J14">
+        <v>-0.3373493975903614</v>
+      </c>
       <c r="K14">
-        <v>-7.05</v>
+        <v>-2.23</v>
+      </c>
+      <c r="L14">
+        <v>-0.5373493975903614</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2139,67 +2172,73 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>1.54</v>
+        <v>0.005</v>
       </c>
       <c r="V14">
-        <v>0.11</v>
+        <v>0.0004950495049504951</v>
       </c>
       <c r="W14">
-        <v>-0.2231012658227848</v>
+        <v>0.7408637873754154</v>
       </c>
       <c r="X14">
-        <v>0.09404034272219189</v>
+        <v>0.08324314272163807</v>
       </c>
       <c r="Y14">
-        <v>-0.3171416085449767</v>
+        <v>0.6576206446537773</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>15.54307116104869</v>
       </c>
       <c r="AA14">
-        <v>-0.2545774647887324</v>
+        <v>-5.243445692883894</v>
       </c>
       <c r="AB14">
-        <v>0.09404034272219189</v>
+        <v>0.08009221249162726</v>
       </c>
       <c r="AC14">
-        <v>-0.3486178075109243</v>
+        <v>-5.323537905375521</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG14">
-        <v>-1.54</v>
+        <v>1.495</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>0.1293103448275862</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>-0.3875968992248062</v>
       </c>
       <c r="AJ14">
-        <v>-0.1235955056179775</v>
+        <v>0.1289348857266063</v>
       </c>
       <c r="AK14">
-        <v>-0.08433734939759036</v>
+        <v>-0.3858064516129033</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>0.163</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>0.163</v>
       </c>
       <c r="AN14">
-        <v>-0</v>
+        <v>-1.2</v>
+      </c>
+      <c r="AO14">
+        <v>-8.588957055214722</v>
       </c>
       <c r="AP14">
-        <v>0.2254758418740849</v>
+        <v>-1.196</v>
+      </c>
+      <c r="AQ14">
+        <v>-8.588957055214722</v>
       </c>
     </row>
     <row r="15">
@@ -2210,7 +2249,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gequity S.p.A. (BIT:GEQ)</t>
+          <t>VAM Investments SPAC B.V. (ENXTAM:VAM)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2218,26 +2257,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D15">
-        <v>0.7809999999999999</v>
-      </c>
-      <c r="G15">
-        <v>-0.5057471264367817</v>
-      </c>
-      <c r="H15">
-        <v>-0.5057471264367817</v>
-      </c>
-      <c r="I15">
-        <v>-0.5632183908045977</v>
-      </c>
-      <c r="J15">
-        <v>-0.5632183908045977</v>
-      </c>
       <c r="K15">
-        <v>-3.19</v>
-      </c>
-      <c r="L15">
-        <v>-0.9166666666666666</v>
+        <v>-8.5</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2261,73 +2282,58 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>0.313</v>
+        <v>0.884</v>
       </c>
       <c r="V15">
-        <v>0.04785932721712538</v>
+        <v>0.003141435678749112</v>
       </c>
       <c r="W15">
-        <v>4.596541786743516</v>
+        <v>-4.146341463414634</v>
       </c>
       <c r="X15">
-        <v>0.1170858704107589</v>
+        <v>0.07873556418937229</v>
       </c>
       <c r="Y15">
-        <v>4.479455916332757</v>
-      </c>
-      <c r="Z15">
-        <v>1.422730989370401</v>
-      </c>
-      <c r="AA15">
-        <v>-0.8013082583810304</v>
+        <v>-4.225077027604007</v>
       </c>
       <c r="AB15">
-        <v>0.09867162588280209</v>
-      </c>
-      <c r="AC15">
-        <v>-0.8999798842638325</v>
+        <v>0.07873556418937229</v>
       </c>
       <c r="AD15">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>3.277</v>
+        <v>-0.884</v>
       </c>
       <c r="AH15">
-        <v>0.3543928923988154</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>6.189655172413792</v>
+        <v>-0</v>
       </c>
       <c r="AJ15">
-        <v>0.3338086991952735</v>
+        <v>-0.003151335396198435</v>
       </c>
       <c r="AK15">
-        <v>12.27340823970038</v>
+        <v>0.1222007188277578</v>
       </c>
       <c r="AL15">
-        <v>0.244</v>
+        <v>11.4</v>
       </c>
       <c r="AM15">
-        <v>0.244</v>
-      </c>
-      <c r="AN15">
-        <v>-1.869791666666667</v>
+        <v>6.640000000000001</v>
       </c>
       <c r="AO15">
-        <v>-8.032786885245901</v>
-      </c>
-      <c r="AP15">
-        <v>-1.706770833333333</v>
+        <v>-0.156140350877193</v>
       </c>
       <c r="AQ15">
-        <v>-8.032786885245901</v>
+        <v>-0.2680722891566265</v>
       </c>
     </row>
     <row r="16">
@@ -2338,7 +2344,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VAM Investments SPAC B.V. (ENXTAM:VAM)</t>
+          <t>H-FARM S.p.A. (BIT:FARM)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2346,8 +2352,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G16">
+        <v>-0.1818414322250639</v>
+      </c>
+      <c r="H16">
+        <v>-0.1818414322250639</v>
+      </c>
+      <c r="I16">
+        <v>-0.2542199488491048</v>
+      </c>
+      <c r="J16">
+        <v>-0.2542199488491048</v>
+      </c>
       <c r="K16">
-        <v>-4.78</v>
+        <v>-9.640000000000001</v>
+      </c>
+      <c r="L16">
+        <v>-0.2465473145780051</v>
       </c>
       <c r="M16">
         <v>-0</v>
@@ -2371,16 +2392,22 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>2.58</v>
+        <v>11</v>
       </c>
       <c r="V16">
-        <v>0.009416058394160584</v>
+        <v>0.4977375565610859</v>
+      </c>
+      <c r="W16">
+        <v>-8.16949152542373</v>
       </c>
       <c r="X16">
-        <v>0.09404034272219189</v>
+        <v>0.07873556418937229</v>
+      </c>
+      <c r="Y16">
+        <v>-8.248227089613103</v>
       </c>
       <c r="AB16">
-        <v>0.09404034272219189</v>
+        <v>0.07873556418937229</v>
       </c>
       <c r="AD16">
         <v>0</v>
@@ -2392,7 +2419,7 @@
         <v>0</v>
       </c>
       <c r="AG16">
-        <v>-2.58</v>
+        <v>-11</v>
       </c>
       <c r="AH16">
         <v>0</v>
@@ -2401,22 +2428,25 @@
         <v>0</v>
       </c>
       <c r="AJ16">
-        <v>-0.009505563333578954</v>
+        <v>-0.9909909909909909</v>
       </c>
       <c r="AK16">
-        <v>4.867924528301884</v>
+        <v>4.313725490196077</v>
       </c>
       <c r="AL16">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>6.095000000000001</v>
-      </c>
-      <c r="AO16">
-        <v>-0.2291325695581014</v>
+        <v>-2.3</v>
+      </c>
+      <c r="AN16">
+        <v>-0</v>
+      </c>
+      <c r="AP16">
+        <v>1.547116736990155</v>
       </c>
       <c r="AQ16">
-        <v>-0.2296964725184577</v>
+        <v>4.321739130434783</v>
       </c>
     </row>
   </sheetData>
